--- a/02.06.2026/optimizationMethods/Practice/Lab7/Tasks.xlsx
+++ b/02.06.2026/optimizationMethods/Practice/Lab7/Tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rameshkamir\Study\vyatsu_works\02.06.2026\optimizationMethods\Practice\Lab7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFE972A-ABDF-4B2B-B77C-65FEA9425FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB76A804-DDDD-44A0-8E32-199E21837DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="8" xr2:uid="{2E4FEE15-A35B-405B-BDE9-F94D16F1D2DA}"/>
   </bookViews>
